--- a/resources/report/60/95/rpt_6095160.xlsx
+++ b/resources/report/60/95/rpt_6095160.xlsx
@@ -33,9 +33,6 @@
     <t>Mã số thuế: $[TAX_CODE]</t>
   </si>
   <si>
-    <t>BẢNG KÊ HÓA ĐƠN XÓA BỎ</t>
-  </si>
-  <si>
     <t>$[DATE_FROM]</t>
   </si>
   <si>
@@ -107,9 +104,6 @@
     <t>SIGN_DT</t>
   </si>
   <si>
-    <t xml:space="preserve"> AMOUNT </t>
-  </si>
-  <si>
     <t>CUS_CD</t>
   </si>
   <si>
@@ -132,15 +126,22 @@
   </si>
   <si>
     <t>Tổng số hóa đơn trên bảng kê:$[L_COUNT_ORDER] hóa đơn</t>
+  </si>
+  <si>
+    <t>AMOUNT1</t>
+  </si>
+  <si>
+    <t>$[TITLE_INVOICE]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -241,7 +242,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -283,6 +284,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -298,6 +306,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -306,9 +317,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -596,6 +604,10 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" customWidth="1"/>
     <col min="9" max="9" width="13.42578125" customWidth="1"/>
     <col min="10" max="10" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
@@ -605,60 +617,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="3"/>
       <c r="K1" s="2"/>
       <c r="L1" s="4"/>
-      <c r="M1" s="21" t="s">
+      <c r="M1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="21"/>
+      <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="22"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -678,7 +690,7 @@
     </row>
     <row r="5" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="B5" s="23"/>
       <c r="C5" s="23"/>
@@ -695,147 +707,147 @@
       <c r="N5" s="23"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="15"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="16"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="B8" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19" t="s">
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="17" t="s">
+      <c r="M8" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="M8" s="17" t="s">
+      <c r="N8" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="N8" s="17" t="s">
+    </row>
+    <row r="9" spans="1:14" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="20"/>
+      <c r="B9" s="12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
-      <c r="B9" s="12" t="s">
+      <c r="C9" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="D9" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="E9" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="F9" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="G9" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="H9" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="I9" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="J9" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="K9" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="K9" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="K10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="M10" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="N10" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -843,15 +855,15 @@
       <c r="B11" s="9"/>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
       <c r="G11" s="11"/>
       <c r="H11" s="8"/>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
       <c r="L11" s="10"/>
-      <c r="M11" s="8"/>
+      <c r="M11" s="17"/>
       <c r="N11" s="9"/>
     </row>
   </sheetData>
@@ -872,5 +884,6 @@
     <mergeCell ref="N8:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/resources/report/60/95/rpt_6095160.xlsx
+++ b/resources/report/60/95/rpt_6095160.xlsx
@@ -131,7 +131,7 @@
     <t>AMOUNT1</t>
   </si>
   <si>
-    <t>$[TITLE_INVOICE]</t>
+    <t>BẢNG KÊ HÓA ĐƠN XÓA BỎ</t>
   </si>
 </sst>
 </file>
